--- a/data/grades/supply_emlyon.xlsx
+++ b/data/grades/supply_emlyon.xlsx
@@ -1,43 +1,108 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillaumemetzler/Documents/GuillaumeMetzler.github.io/data/grades/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7357C48B-03F3-CE4C-BC1B-0B47AC205781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="15860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="notes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="notes" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>annee</t>
+  </si>
+  <si>
+    <t>Examen</t>
+  </si>
+  <si>
+    <t>Projet</t>
+  </si>
+  <si>
+    <t>Moyenne</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -45,88 +110,136 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="27">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -414,28 +527,2209 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D150"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col min="1" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>annee</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
+    <row r="1" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="5">
+        <v>2023</v>
+      </c>
+      <c r="B2" s="6">
+        <v>8</v>
+      </c>
+      <c r="C2" s="6">
+        <v>12</v>
+      </c>
+      <c r="D2" s="7">
+        <f>0.33*B2+0.67*C2</f>
+        <v>10.680000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B3" s="3">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3">
+        <v>11</v>
+      </c>
+      <c r="D3" s="9">
+        <f t="shared" ref="D3:D43" si="0">0.33*B3+0.67*C3</f>
+        <v>10.01</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B4" s="3">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3">
+        <v>13</v>
+      </c>
+      <c r="D4" s="9">
+        <f t="shared" si="0"/>
+        <v>12.340000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B5" s="3">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3">
+        <v>14</v>
+      </c>
+      <c r="D5" s="9">
+        <f t="shared" si="0"/>
+        <v>14.66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B6" s="3">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3">
+        <v>14</v>
+      </c>
+      <c r="D6" s="9">
+        <f t="shared" si="0"/>
+        <v>13.670000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B7" s="3">
+        <v>11</v>
+      </c>
+      <c r="C7" s="3">
+        <v>13</v>
+      </c>
+      <c r="D7" s="9">
+        <f t="shared" si="0"/>
+        <v>12.340000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B8" s="3">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3">
+        <v>10</v>
+      </c>
+      <c r="D8" s="9">
+        <f t="shared" si="0"/>
+        <v>10.33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B9" s="3">
+        <v>13</v>
+      </c>
+      <c r="C9" s="3">
+        <v>8</v>
+      </c>
+      <c r="D9" s="9">
+        <f t="shared" si="0"/>
+        <v>9.65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B10" s="3">
+        <v>14</v>
+      </c>
+      <c r="C10" s="3">
+        <v>16</v>
+      </c>
+      <c r="D10" s="9">
+        <f t="shared" si="0"/>
+        <v>15.34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B11" s="3">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3">
+        <v>14</v>
+      </c>
+      <c r="D11" s="9">
+        <f t="shared" si="0"/>
+        <v>14.330000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B12" s="3">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3">
+        <v>8</v>
+      </c>
+      <c r="D12" s="9">
+        <f t="shared" si="0"/>
+        <v>9.32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B13" s="3">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3">
+        <v>9</v>
+      </c>
+      <c r="D13" s="9">
+        <f t="shared" si="0"/>
+        <v>9.66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B14" s="3">
+        <v>9</v>
+      </c>
+      <c r="C14" s="3">
+        <v>13</v>
+      </c>
+      <c r="D14" s="9">
+        <f t="shared" si="0"/>
+        <v>11.680000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B15" s="3">
+        <v>11</v>
+      </c>
+      <c r="C15" s="3">
+        <v>11</v>
+      </c>
+      <c r="D15" s="9">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B16" s="3">
+        <v>11</v>
+      </c>
+      <c r="C16" s="3">
+        <v>6</v>
+      </c>
+      <c r="D16" s="9">
+        <f t="shared" si="0"/>
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B17" s="3">
+        <v>14</v>
+      </c>
+      <c r="C17" s="3">
+        <v>15</v>
+      </c>
+      <c r="D17" s="9">
+        <f t="shared" si="0"/>
+        <v>14.670000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B18" s="3">
+        <v>12</v>
+      </c>
+      <c r="C18" s="3">
+        <v>13.5</v>
+      </c>
+      <c r="D18" s="9">
+        <f t="shared" si="0"/>
+        <v>13.004999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B19" s="3">
+        <v>12</v>
+      </c>
+      <c r="C19" s="3">
+        <v>12</v>
+      </c>
+      <c r="D19" s="9">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B20" s="3">
+        <v>12</v>
+      </c>
+      <c r="C20" s="3">
+        <v>9</v>
+      </c>
+      <c r="D20" s="9">
+        <f t="shared" si="0"/>
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B21" s="3">
+        <v>13</v>
+      </c>
+      <c r="C21" s="3">
+        <v>14</v>
+      </c>
+      <c r="D21" s="9">
+        <f t="shared" si="0"/>
+        <v>13.670000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B22" s="3">
+        <v>20</v>
+      </c>
+      <c r="C22" s="3">
+        <v>18</v>
+      </c>
+      <c r="D22" s="9">
+        <f t="shared" si="0"/>
+        <v>18.66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B23" s="3">
+        <v>7</v>
+      </c>
+      <c r="C23" s="3">
+        <v>11</v>
+      </c>
+      <c r="D23" s="9">
+        <f t="shared" si="0"/>
+        <v>9.68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B24" s="3">
+        <v>8</v>
+      </c>
+      <c r="C24" s="3">
+        <v>10</v>
+      </c>
+      <c r="D24" s="9">
+        <f t="shared" si="0"/>
+        <v>9.34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B25" s="3">
+        <v>11</v>
+      </c>
+      <c r="C25" s="3">
+        <v>10</v>
+      </c>
+      <c r="D25" s="9">
+        <f t="shared" si="0"/>
+        <v>10.33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B26" s="4">
+        <v>10</v>
+      </c>
+      <c r="C26" s="3">
+        <v>14</v>
+      </c>
+      <c r="D26" s="9">
+        <f t="shared" si="0"/>
+        <v>12.680000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B27" s="3">
+        <v>12</v>
+      </c>
+      <c r="C27" s="3">
+        <v>9</v>
+      </c>
+      <c r="D27" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B28" s="3">
+        <v>12</v>
+      </c>
+      <c r="C28" s="3">
+        <v>14</v>
+      </c>
+      <c r="D28" s="9">
+        <f t="shared" si="0"/>
+        <v>13.34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B29" s="3">
+        <v>11</v>
+      </c>
+      <c r="C29" s="3">
+        <v>15</v>
+      </c>
+      <c r="D29" s="9">
+        <f t="shared" si="0"/>
+        <v>13.680000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B30" s="3">
+        <v>4</v>
+      </c>
+      <c r="C30" s="3">
+        <v>13</v>
+      </c>
+      <c r="D30" s="9">
+        <f t="shared" si="0"/>
+        <v>10.030000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B31" s="3">
+        <v>10</v>
+      </c>
+      <c r="C31" s="3">
+        <v>16</v>
+      </c>
+      <c r="D31" s="9">
+        <f t="shared" si="0"/>
+        <v>14.020000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B32" s="3">
+        <v>13</v>
+      </c>
+      <c r="C32" s="3">
+        <v>14</v>
+      </c>
+      <c r="D32" s="9">
+        <f t="shared" si="0"/>
+        <v>13.670000000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B33" s="3">
+        <v>5</v>
+      </c>
+      <c r="C33" s="3">
+        <v>13</v>
+      </c>
+      <c r="D33" s="9">
+        <f t="shared" si="0"/>
+        <v>10.360000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B34" s="3">
+        <v>11</v>
+      </c>
+      <c r="C34" s="3">
+        <v>15</v>
+      </c>
+      <c r="D34" s="9">
+        <f>0.33*B34+0.67*C34</f>
+        <v>13.680000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B35" s="3">
+        <v>14</v>
+      </c>
+      <c r="C35" s="3">
+        <v>14</v>
+      </c>
+      <c r="D35" s="9">
+        <f>0.33*B35+0.67*C35</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B36" s="3">
+        <v>14</v>
+      </c>
+      <c r="C36" s="3">
+        <v>16</v>
+      </c>
+      <c r="D36" s="9">
+        <f t="shared" si="0"/>
+        <v>15.34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B37" s="3">
+        <v>10</v>
+      </c>
+      <c r="C37" s="3">
+        <v>14</v>
+      </c>
+      <c r="D37" s="9">
+        <f t="shared" si="0"/>
+        <v>12.680000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B38" s="3">
+        <v>12</v>
+      </c>
+      <c r="C38" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="D38" s="9">
+        <f t="shared" si="0"/>
+        <v>13.675000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B39" s="3">
+        <v>14</v>
+      </c>
+      <c r="C39" s="3">
+        <v>16</v>
+      </c>
+      <c r="D39" s="9">
+        <f t="shared" si="0"/>
+        <v>15.34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B40" s="3">
+        <v>9</v>
+      </c>
+      <c r="C40" s="3">
+        <v>11</v>
+      </c>
+      <c r="D40" s="9">
+        <f t="shared" si="0"/>
+        <v>10.34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B41" s="3">
+        <v>11</v>
+      </c>
+      <c r="C41" s="3">
+        <v>11</v>
+      </c>
+      <c r="D41" s="9">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B42" s="3">
+        <v>11</v>
+      </c>
+      <c r="C42" s="3">
+        <v>14</v>
+      </c>
+      <c r="D42" s="9">
+        <f t="shared" si="0"/>
+        <v>13.010000000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="10">
+        <v>2023</v>
+      </c>
+      <c r="B43" s="11">
+        <v>12</v>
+      </c>
+      <c r="C43" s="11">
+        <v>12</v>
+      </c>
+      <c r="D43" s="12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="14">
+        <v>2024</v>
+      </c>
+      <c r="B44" s="6">
+        <v>15</v>
+      </c>
+      <c r="C44" s="6">
+        <v>19</v>
+      </c>
+      <c r="D44" s="15">
+        <f t="shared" ref="D44:D51" si="1">0.25*B44+0.75*C44</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B45" s="3">
+        <v>19</v>
+      </c>
+      <c r="C45" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="D45" s="16">
+        <f t="shared" si="1"/>
+        <v>16.375</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B46" s="3">
+        <v>16.5</v>
+      </c>
+      <c r="C46" s="3">
+        <v>15</v>
+      </c>
+      <c r="D46" s="16">
+        <f t="shared" si="1"/>
+        <v>15.375</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B47" s="3">
+        <v>16</v>
+      </c>
+      <c r="C47" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="D47" s="16">
+        <f t="shared" si="1"/>
+        <v>14.875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B48" s="17">
+        <v>19</v>
+      </c>
+      <c r="C48" s="3">
+        <v>17.5</v>
+      </c>
+      <c r="D48" s="16">
+        <f t="shared" si="1"/>
+        <v>17.875</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B49" s="3">
+        <v>16.5</v>
+      </c>
+      <c r="C49" s="3">
+        <v>15</v>
+      </c>
+      <c r="D49" s="16">
+        <f t="shared" si="1"/>
+        <v>15.375</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B50" s="3">
+        <v>18</v>
+      </c>
+      <c r="C50" s="3">
+        <v>18.5</v>
+      </c>
+      <c r="D50" s="16">
+        <f t="shared" si="1"/>
+        <v>18.375</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B51" s="3">
+        <v>18</v>
+      </c>
+      <c r="C51" s="3">
+        <v>16</v>
+      </c>
+      <c r="D51" s="16">
+        <f t="shared" si="1"/>
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B52" s="3">
+        <v>15</v>
+      </c>
+      <c r="C52" s="3">
+        <v>15</v>
+      </c>
+      <c r="D52" s="16">
+        <f>0.25*B52+0.75*C52</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B53" s="3">
+        <v>19.5</v>
+      </c>
+      <c r="C53" s="3">
+        <v>18</v>
+      </c>
+      <c r="D53" s="16">
+        <f t="shared" ref="D53:D100" si="2">0.25*B53+0.75*C53</f>
+        <v>18.375</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B54" s="3">
+        <v>18.5</v>
+      </c>
+      <c r="C54" s="3">
+        <v>17</v>
+      </c>
+      <c r="D54" s="16">
+        <f t="shared" si="2"/>
+        <v>17.375</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B55" s="3">
+        <v>16</v>
+      </c>
+      <c r="C55" s="3">
+        <v>15</v>
+      </c>
+      <c r="D55" s="16">
+        <f t="shared" si="2"/>
+        <v>15.25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B56" s="3">
+        <v>16</v>
+      </c>
+      <c r="C56" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="D56" s="16">
+        <f t="shared" si="2"/>
+        <v>14.875</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B57" s="3">
+        <v>18</v>
+      </c>
+      <c r="C57" s="3">
+        <v>13.5</v>
+      </c>
+      <c r="D57" s="16">
+        <f t="shared" si="2"/>
+        <v>14.625</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B58" s="3">
+        <v>17.5</v>
+      </c>
+      <c r="C58" s="3">
+        <v>17.5</v>
+      </c>
+      <c r="D58" s="16">
+        <f t="shared" si="2"/>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B59" s="3">
+        <v>18.5</v>
+      </c>
+      <c r="C59" s="3">
+        <v>13.5</v>
+      </c>
+      <c r="D59" s="16">
+        <f t="shared" si="2"/>
+        <v>14.75</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B60" s="3">
+        <v>19.5</v>
+      </c>
+      <c r="C60" s="3">
+        <v>16.5</v>
+      </c>
+      <c r="D60" s="16">
+        <f t="shared" si="2"/>
+        <v>17.25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B61" s="3">
+        <v>17.5</v>
+      </c>
+      <c r="C61" s="3">
+        <v>15</v>
+      </c>
+      <c r="D61" s="16">
+        <f t="shared" si="2"/>
+        <v>15.625</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B62" s="3">
+        <v>15</v>
+      </c>
+      <c r="C62" s="3">
+        <v>12</v>
+      </c>
+      <c r="D62" s="16">
+        <f t="shared" si="2"/>
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B63" s="3">
+        <v>18</v>
+      </c>
+      <c r="C63" s="3">
+        <v>15</v>
+      </c>
+      <c r="D63" s="16">
+        <f t="shared" si="2"/>
+        <v>15.75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B64" s="3">
+        <v>16</v>
+      </c>
+      <c r="C64" s="3">
+        <v>16</v>
+      </c>
+      <c r="D64" s="16">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B65" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="C65" s="3">
+        <v>15</v>
+      </c>
+      <c r="D65" s="16">
+        <f t="shared" si="2"/>
+        <v>14.875</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B66" s="3">
+        <v>16.5</v>
+      </c>
+      <c r="C66" s="3">
+        <v>12</v>
+      </c>
+      <c r="D66" s="16">
+        <f t="shared" si="2"/>
+        <v>13.125</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B67" s="3">
+        <v>15</v>
+      </c>
+      <c r="C67" s="3">
+        <v>9</v>
+      </c>
+      <c r="D67" s="16">
+        <f t="shared" si="2"/>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B68" s="3">
+        <v>17</v>
+      </c>
+      <c r="C68" s="3">
+        <v>16.5</v>
+      </c>
+      <c r="D68" s="16">
+        <f t="shared" si="2"/>
+        <v>16.625</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B69" s="3">
+        <v>16</v>
+      </c>
+      <c r="C69" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="D69" s="16">
+        <f t="shared" si="2"/>
+        <v>14.875</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B70" s="3">
+        <v>18</v>
+      </c>
+      <c r="C70" s="3">
+        <v>17.5</v>
+      </c>
+      <c r="D70" s="16">
+        <f t="shared" si="2"/>
+        <v>17.625</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B71" s="3">
+        <v>17</v>
+      </c>
+      <c r="C71" s="3">
+        <v>9</v>
+      </c>
+      <c r="D71" s="16">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B72" s="3">
+        <v>17.5</v>
+      </c>
+      <c r="C72" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="D72" s="16">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B73" s="3">
+        <v>16</v>
+      </c>
+      <c r="C73" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="D73" s="16">
+        <f t="shared" si="2"/>
+        <v>14.875</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B74" s="3">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3">
+        <v>0</v>
+      </c>
+      <c r="D74" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B75" s="3">
+        <v>19</v>
+      </c>
+      <c r="C75" s="3">
+        <v>18</v>
+      </c>
+      <c r="D75" s="16">
+        <f t="shared" si="2"/>
+        <v>18.25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B76" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="C76" s="3">
+        <v>15</v>
+      </c>
+      <c r="D76" s="16">
+        <f t="shared" si="2"/>
+        <v>15.125</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B77" s="3">
+        <v>19</v>
+      </c>
+      <c r="C77" s="3">
+        <v>16</v>
+      </c>
+      <c r="D77" s="16">
+        <f t="shared" si="2"/>
+        <v>16.75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B78" s="3">
+        <v>17</v>
+      </c>
+      <c r="C78" s="3">
+        <v>14</v>
+      </c>
+      <c r="D78" s="16">
+        <f t="shared" si="2"/>
+        <v>14.75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B79" s="3">
+        <v>17</v>
+      </c>
+      <c r="C79" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="D79" s="16">
+        <f t="shared" si="2"/>
+        <v>15.125</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B80" s="3">
+        <v>19</v>
+      </c>
+      <c r="C80" s="3">
+        <v>16.5</v>
+      </c>
+      <c r="D80" s="16">
+        <f t="shared" si="2"/>
+        <v>17.125</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B81" s="3">
+        <v>18.5</v>
+      </c>
+      <c r="C81" s="3">
+        <v>17</v>
+      </c>
+      <c r="D81" s="16">
+        <f t="shared" si="2"/>
+        <v>17.375</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B82" s="3">
+        <v>18</v>
+      </c>
+      <c r="C82" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="D82" s="16">
+        <f t="shared" si="2"/>
+        <v>16.125</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B83" s="3">
+        <v>17.5</v>
+      </c>
+      <c r="C83" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="D83" s="16">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B84" s="3">
+        <v>20</v>
+      </c>
+      <c r="C84" s="3">
+        <v>18</v>
+      </c>
+      <c r="D84" s="16">
+        <f t="shared" si="2"/>
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B85" s="3">
+        <v>14</v>
+      </c>
+      <c r="C85" s="3">
+        <v>13</v>
+      </c>
+      <c r="D85" s="16">
+        <f t="shared" si="2"/>
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B86" s="3">
+        <v>17</v>
+      </c>
+      <c r="C86" s="3">
+        <v>16.5</v>
+      </c>
+      <c r="D86" s="16">
+        <f t="shared" si="2"/>
+        <v>16.625</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B87" s="3">
+        <v>19</v>
+      </c>
+      <c r="C87" s="3">
+        <v>16</v>
+      </c>
+      <c r="D87" s="16">
+        <f t="shared" si="2"/>
+        <v>16.75</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B88" s="3">
+        <v>16.5</v>
+      </c>
+      <c r="C88" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="D88" s="16">
+        <f t="shared" si="2"/>
+        <v>15.75</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B89" s="3">
+        <v>15</v>
+      </c>
+      <c r="C89" s="3">
+        <v>15</v>
+      </c>
+      <c r="D89" s="16">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B90" s="3">
+        <v>18.5</v>
+      </c>
+      <c r="C90" s="3">
+        <v>17</v>
+      </c>
+      <c r="D90" s="16">
+        <f t="shared" si="2"/>
+        <v>17.375</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B91" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="C91" s="3">
+        <v>17</v>
+      </c>
+      <c r="D91" s="16">
+        <f t="shared" si="2"/>
+        <v>16.625</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B92" s="3">
+        <v>18</v>
+      </c>
+      <c r="C92" s="3">
+        <v>15</v>
+      </c>
+      <c r="D92" s="16">
+        <f t="shared" si="2"/>
+        <v>15.75</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B93" s="3">
+        <v>19</v>
+      </c>
+      <c r="C93" s="3">
+        <v>8</v>
+      </c>
+      <c r="D93" s="16">
+        <f t="shared" si="2"/>
+        <v>10.75</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B94" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="C94" s="3">
+        <v>13</v>
+      </c>
+      <c r="D94" s="16">
+        <f t="shared" si="2"/>
+        <v>13.625</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B95" s="3">
+        <v>17</v>
+      </c>
+      <c r="C95" s="3">
+        <v>16.5</v>
+      </c>
+      <c r="D95" s="16">
+        <f t="shared" si="2"/>
+        <v>16.625</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B96" s="3">
+        <v>19</v>
+      </c>
+      <c r="C96" s="3">
+        <v>14</v>
+      </c>
+      <c r="D96" s="16">
+        <f t="shared" si="2"/>
+        <v>15.25</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A97" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B97" s="3">
+        <v>16</v>
+      </c>
+      <c r="C97" s="3">
+        <v>15</v>
+      </c>
+      <c r="D97" s="16">
+        <f t="shared" si="2"/>
+        <v>15.25</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B98" s="3">
+        <v>18</v>
+      </c>
+      <c r="C98" s="3">
+        <v>16</v>
+      </c>
+      <c r="D98" s="16">
+        <f t="shared" si="2"/>
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B99" s="3">
+        <v>19</v>
+      </c>
+      <c r="C99" s="3">
+        <v>15</v>
+      </c>
+      <c r="D99" s="16">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="18">
+        <v>2024</v>
+      </c>
+      <c r="B100" s="11">
+        <v>15.5</v>
+      </c>
+      <c r="C100" s="11">
+        <v>10</v>
+      </c>
+      <c r="D100" s="19">
+        <f t="shared" si="2"/>
+        <v>11.375</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A101" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B101" s="20">
+        <v>8</v>
+      </c>
+      <c r="C101" s="20">
+        <v>13</v>
+      </c>
+      <c r="D101" s="21">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A102" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B102" s="22">
+        <v>16</v>
+      </c>
+      <c r="C102" s="22">
+        <v>17</v>
+      </c>
+      <c r="D102" s="23">
+        <v>16.66</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A103" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B103" s="22">
+        <v>6</v>
+      </c>
+      <c r="C103" s="22">
+        <v>15</v>
+      </c>
+      <c r="D103" s="23">
+        <v>11.94</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A104" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B104" s="22">
+        <v>12</v>
+      </c>
+      <c r="C104" s="22">
+        <v>15</v>
+      </c>
+      <c r="D104" s="23">
+        <v>13.98</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A105" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B105" s="22">
+        <v>10</v>
+      </c>
+      <c r="C105" s="22">
+        <v>11</v>
+      </c>
+      <c r="D105" s="23">
+        <v>10.66</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A106" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B106" s="22">
+        <v>4</v>
+      </c>
+      <c r="C106" s="22">
+        <v>16</v>
+      </c>
+      <c r="D106" s="23">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A107" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B107" s="22">
+        <v>10</v>
+      </c>
+      <c r="C107" s="22">
+        <v>14</v>
+      </c>
+      <c r="D107" s="23">
+        <v>12.64</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A108" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B108" s="22">
+        <v>6</v>
+      </c>
+      <c r="C108" s="22">
+        <v>15</v>
+      </c>
+      <c r="D108" s="23">
+        <v>11.94</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A109" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B109" s="22">
+        <v>11</v>
+      </c>
+      <c r="C109" s="22">
+        <v>11</v>
+      </c>
+      <c r="D109" s="23">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A110" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B110" s="22">
+        <v>13</v>
+      </c>
+      <c r="C110" s="22">
+        <v>14.5</v>
+      </c>
+      <c r="D110" s="23">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A111" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B111" s="22">
+        <v>2</v>
+      </c>
+      <c r="C111" s="22">
+        <v>14</v>
+      </c>
+      <c r="D111" s="23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A112" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B112" s="24">
+        <v>0</v>
+      </c>
+      <c r="C112" s="22">
+        <v>15</v>
+      </c>
+      <c r="D112" s="23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A113" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B113" s="22">
+        <v>4</v>
+      </c>
+      <c r="C113" s="22">
+        <v>14</v>
+      </c>
+      <c r="D113" s="23">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A114" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B114" s="22">
+        <v>2</v>
+      </c>
+      <c r="C114" s="22">
+        <v>14</v>
+      </c>
+      <c r="D114" s="23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A115" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B115" s="22">
+        <v>13</v>
+      </c>
+      <c r="C115" s="22">
+        <v>16</v>
+      </c>
+      <c r="D115" s="23">
+        <v>14.98</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A116" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B116" s="22">
+        <v>14</v>
+      </c>
+      <c r="C116" s="22">
+        <v>14.5</v>
+      </c>
+      <c r="D116" s="23">
+        <v>14.33</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A117" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B117" s="22">
+        <v>7</v>
+      </c>
+      <c r="C117" s="22">
+        <v>16</v>
+      </c>
+      <c r="D117" s="23">
+        <v>12.94</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A118" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B118" s="22">
+        <v>11</v>
+      </c>
+      <c r="C118" s="22">
+        <v>13.5</v>
+      </c>
+      <c r="D118" s="23">
+        <v>12.65</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A119" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B119" s="22">
+        <v>13</v>
+      </c>
+      <c r="C119" s="22">
+        <v>15</v>
+      </c>
+      <c r="D119" s="23">
+        <v>14.32</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A120" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B120" s="22">
+        <v>10</v>
+      </c>
+      <c r="C120" s="22">
+        <v>14.5</v>
+      </c>
+      <c r="D120" s="23">
+        <v>12.97</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A121" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B121" s="22">
+        <v>14</v>
+      </c>
+      <c r="C121" s="22">
+        <v>15</v>
+      </c>
+      <c r="D121" s="23">
+        <v>14.66</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A122" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B122" s="22">
+        <v>13</v>
+      </c>
+      <c r="C122" s="22">
+        <v>16</v>
+      </c>
+      <c r="D122" s="23">
+        <v>14.98</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A123" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B123" s="22">
+        <v>16</v>
+      </c>
+      <c r="C123" s="22">
+        <v>16.5</v>
+      </c>
+      <c r="D123" s="23">
+        <v>16.329999999999998</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A124" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B124" s="22">
+        <v>15</v>
+      </c>
+      <c r="C124" s="22">
+        <v>16</v>
+      </c>
+      <c r="D124" s="23">
+        <v>15.66</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A125" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B125" s="22">
+        <v>15</v>
+      </c>
+      <c r="C125" s="22">
+        <v>15.5</v>
+      </c>
+      <c r="D125" s="23">
+        <v>15.33</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A126" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B126" s="22">
+        <v>1</v>
+      </c>
+      <c r="C126" s="22">
+        <v>15</v>
+      </c>
+      <c r="D126" s="23">
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A127" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B127" s="22">
+        <v>4</v>
+      </c>
+      <c r="C127" s="22">
+        <v>15</v>
+      </c>
+      <c r="D127" s="23">
+        <v>11.26</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A128" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B128" s="22">
+        <v>11</v>
+      </c>
+      <c r="C128" s="22">
+        <v>15</v>
+      </c>
+      <c r="D128" s="23">
+        <v>13.64</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A129" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B129" s="22">
+        <v>0</v>
+      </c>
+      <c r="C129" s="22">
+        <v>15</v>
+      </c>
+      <c r="D129" s="23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A130" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B130" s="22">
+        <v>9</v>
+      </c>
+      <c r="C130" s="22">
+        <v>13.5</v>
+      </c>
+      <c r="D130" s="23">
+        <v>11.97</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A131" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B131" s="24">
+        <v>0</v>
+      </c>
+      <c r="C131" s="22">
+        <v>15</v>
+      </c>
+      <c r="D131" s="23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A132" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B132" s="22">
+        <v>12</v>
+      </c>
+      <c r="C132" s="22">
+        <v>14</v>
+      </c>
+      <c r="D132" s="23">
+        <v>13.32</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A133" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B133" s="22">
+        <v>5</v>
+      </c>
+      <c r="C133" s="22">
+        <v>14</v>
+      </c>
+      <c r="D133" s="23">
+        <v>10.94</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A134" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B134" s="22">
+        <v>8</v>
+      </c>
+      <c r="C134" s="22">
+        <v>15</v>
+      </c>
+      <c r="D134" s="23">
+        <v>12.62</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A135" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B135" s="22">
+        <v>13</v>
+      </c>
+      <c r="C135" s="22">
+        <v>16.5</v>
+      </c>
+      <c r="D135" s="23">
+        <v>15.31</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A136" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B136" s="22">
+        <v>9</v>
+      </c>
+      <c r="C136" s="22">
+        <v>13.5</v>
+      </c>
+      <c r="D136" s="23">
+        <v>11.97</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A137" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B137" s="22">
+        <v>11</v>
+      </c>
+      <c r="C137" s="22">
+        <v>14.5</v>
+      </c>
+      <c r="D137" s="23">
+        <v>13.31</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A138" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B138" s="22">
+        <v>13</v>
+      </c>
+      <c r="C138" s="22">
+        <v>16.5</v>
+      </c>
+      <c r="D138" s="23">
+        <v>15.31</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A139" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B139" s="22">
+        <v>8</v>
+      </c>
+      <c r="C139" s="22">
+        <v>13</v>
+      </c>
+      <c r="D139" s="23">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A140" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B140" s="22">
+        <v>20</v>
+      </c>
+      <c r="C140" s="22">
+        <v>19</v>
+      </c>
+      <c r="D140" s="23">
+        <v>19.34</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A141" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B141" s="22">
+        <v>9</v>
+      </c>
+      <c r="C141" s="22">
+        <v>14</v>
+      </c>
+      <c r="D141" s="23">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A142" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B142" s="22">
+        <v>5</v>
+      </c>
+      <c r="C142" s="22">
+        <v>13</v>
+      </c>
+      <c r="D142" s="23">
+        <v>10.28</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A143" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B143" s="22">
+        <v>10.5</v>
+      </c>
+      <c r="C143" s="22">
+        <v>15</v>
+      </c>
+      <c r="D143" s="23">
+        <v>13.47</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A144" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B144" s="22">
+        <v>13</v>
+      </c>
+      <c r="C144" s="22">
+        <v>15.5</v>
+      </c>
+      <c r="D144" s="23">
+        <v>14.65</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A145" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B145" s="22">
+        <v>11</v>
+      </c>
+      <c r="C145" s="22">
+        <v>13</v>
+      </c>
+      <c r="D145" s="23">
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A146" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B146" s="22">
+        <v>13</v>
+      </c>
+      <c r="C146" s="22">
+        <v>19</v>
+      </c>
+      <c r="D146" s="23">
+        <v>16.96</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A147" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B147" s="22">
+        <v>11</v>
+      </c>
+      <c r="C147" s="22">
+        <v>15</v>
+      </c>
+      <c r="D147" s="23">
+        <v>13.64</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A148" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B148" s="22">
+        <v>17</v>
+      </c>
+      <c r="C148" s="22">
+        <v>17</v>
+      </c>
+      <c r="D148" s="23">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A149" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B149" s="22">
+        <v>16</v>
+      </c>
+      <c r="C149" s="22">
+        <v>16</v>
+      </c>
+      <c r="D149" s="23">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="18">
+        <v>2025</v>
+      </c>
+      <c r="B150" s="25">
+        <v>18</v>
+      </c>
+      <c r="C150" s="25">
+        <v>17</v>
+      </c>
+      <c r="D150" s="26">
+        <v>17.34</v>
       </c>
     </row>
   </sheetData>
